--- a/preperation.xlsx
+++ b/preperation.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Git\MOFC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377BAC79-5026-47AA-A338-6ED791F865D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB5D9F6-4E1A-44C3-8B2E-5436C04ACC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="before" sheetId="3" r:id="rId1"/>
+    <sheet name="during" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
   <si>
     <t>BMA-Male to FMA female</t>
   </si>
@@ -82,6 +84,39 @@
   </si>
   <si>
     <t>verify TF1 assignment cases</t>
+  </si>
+  <si>
+    <t>What happens exactly at reset, what happens to LO, Swicth, DCA etc are they also returns to theere default satts</t>
+  </si>
+  <si>
+    <t>what is the lock time for the LO instead we do not cahnge the frequency betwenn 2 setup, e.g we issue same setup just change DCA's</t>
+  </si>
+  <si>
+    <t>what is the minimum gap between 2 sequences of SPI write/read</t>
+  </si>
+  <si>
+    <t>Reset behaviour</t>
+  </si>
+  <si>
+    <t>power status</t>
+  </si>
+  <si>
+    <t>is it impemnetd?? How ti works</t>
+  </si>
+  <si>
+    <t>LO Lock time when unchange</t>
+  </si>
+  <si>
+    <t>Minimum gap between SPI transactions</t>
+  </si>
+  <si>
+    <t>information of buffers (RS422 buffers) at the digital card is it AM26Lv31ID, and AM26LV32ID</t>
+  </si>
+  <si>
+    <t>what connector do you usr  for  at the test-jig -&gt; tMOFC ontrol</t>
+  </si>
+  <si>
+    <t>Test JIg connector info</t>
   </si>
 </sst>
 </file>
@@ -105,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -128,17 +163,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -158,6 +245,192 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>613905</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>46653</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D51DBFFD-5BA1-469D-971F-960340158FDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4600575" y="4581525"/>
+          <a:ext cx="14866667" cy="7771428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>481854</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>216887</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>52377</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3512F70-2374-78EA-4FD8-8FF681137436}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3675530" y="2924735"/>
+          <a:ext cx="8542857" cy="6809524"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>613905</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>46653</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BBE7B1E-5345-4E90-8713-EEB39F38BE10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4600575" y="3314700"/>
+          <a:ext cx="14872830" cy="7771428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>605117</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>100852</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5270739</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>97200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7C1DD02-BEAC-4E6C-BC73-92D28370361F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="605117" y="4263277"/>
+          <a:ext cx="8542297" cy="6873398"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -468,6 +741,197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF981ADD-7B7A-4DF5-8B45-7D9AEA5E6C39}">
+  <dimension ref="A2:B11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="41.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="115.625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="4"/>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="5"/>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E0F359-562A-40F0-B2EB-4941F2B5A5CA}">
+  <dimension ref="A2:C16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="41.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="115.625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C10" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C15" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C16" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:B4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
